--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251010_201255.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251010_201255.xlsx
@@ -3754,7 +3754,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251010_201255.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251010_201255.xlsx
@@ -3754,7 +3754,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251010_201255.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251010_201255.xlsx
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251010_201255.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251010_201255.xlsx
@@ -6016,7 +6016,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251010_201255.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251010_201255.xlsx
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251010_201255.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251010_201255.xlsx
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251010_201255.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251010_201255.xlsx
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251010_201255.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251010_201255.xlsx
@@ -3754,7 +3754,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251010_201255.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251010_201255.xlsx
@@ -3754,7 +3754,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251010_201255.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251010_201255.xlsx
@@ -6016,7 +6016,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251010_201255.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251010_201255.xlsx
@@ -3754,7 +3754,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251010_201255.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251010_201255.xlsx
@@ -3754,7 +3754,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251010_201255.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251010_201255.xlsx
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251010_201255.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251010_201255.xlsx
@@ -3754,7 +3754,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
